--- a/shared/words/E4_单词汇总.xlsx
+++ b/shared/words/E4_单词汇总.xlsx
@@ -1132,6 +1132,11 @@
           <t>words/einheit4/vorhaben.mp3</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich habe heute viel vor.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1154,6 +1159,11 @@
           <t>words/einheit4/aufstehen.mp3</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich stehe um sieben Uhr auf.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1176,6 +1186,11 @@
           <t>words/einheit4/planen.mp3</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wir planen eine Feier für sie.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1198,6 +1213,11 @@
           <t>words/einheit4/finden.mp3</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er findet keine Stelle.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1220,6 +1240,11 @@
           <t>words/einheit4/meinen.mp3</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich meine, das ist richtig.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1242,6 +1267,11 @@
           <t>words/einheit4/einladen.mp3</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wir laden Freunde ein.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1264,6 +1294,11 @@
           <t>words/einheit4/einkaufen.mp3</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich gehe heute einkaufen.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1286,6 +1321,11 @@
           <t>words/einheit4/bestellen.mp3</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xiaoming bestellt Bratkartoffeln.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1308,6 +1348,11 @@
           <t>words/einheit4/vorschlagen.mp3</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich schlage vor, dass wir ins Kino gehen.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1330,6 +1375,11 @@
           <t>words/einheit4/kochen.mp3</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meine Mutter kocht heute Suppe.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1460,6 +1510,11 @@
           <t>words/einheit4/abholen.mp3</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich hole dich am Bahnhof ab.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1482,6 +1537,11 @@
           <t>words/einheit4/reisen.mp3</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wir reisen gern nach Deutschland.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2106,6 +2166,11 @@
           <t>words/einheit4/Geburtstagskind.mp3</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meine Oma ist heute das Geburtstagskind.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2636,6 +2701,11 @@
           <t>words/einheit4/etwas.mp3</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich möchte etwas essen.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2658,6 +2728,11 @@
           <t>words/einheit4/lieb.mp3</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sie ist sehr lieb.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2680,6 +2755,11 @@
           <t>words/einheit4/nichts.mp3</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich habe nichts gegessen.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2702,6 +2782,11 @@
           <t>words/einheit4/andere.mp3</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wo sind die anderen?</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2724,6 +2809,11 @@
           <t>words/einheit4/genau.mp3</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das ist genau richtig.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2746,6 +2836,11 @@
           <t>words/einheit4/ganz.mp3</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das ist ganz einfach.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2768,6 +2863,11 @@
           <t>words/einheit4/bestimmt.mp3</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das hier ist bestimmt deine Oma.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2790,6 +2890,11 @@
           <t>words/einheit4/richtig.mp3</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das ist richtig.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3109,6 +3214,11 @@
           <t>words/einheit4/arbeitslos.mp3</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er ist seit einem Jahr arbeitslos.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3131,6 +3241,11 @@
           <t>words/einheit4/zufrieden.mp3</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich bin mit dem Ergebnis zufrieden.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3153,6 +3268,11 @@
           <t>words/einheit4/als.mp3</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich möchte eine Suppe als Vorspeise.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3175,6 +3295,11 @@
           <t>words/einheit4/fest.mp3</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er hat eine feste Freundin.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3195,6 +3320,11 @@
       <c r="F72" t="inlineStr">
         <is>
           <t>words/einheit4/normal.mp3</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das ist ganz normal.</t>
         </is>
       </c>
     </row>
